--- a/企画書＆仕様書/真仕様書.xlsx
+++ b/企画書＆仕様書/真仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t xml:space="preserve">仕様書</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t xml:space="preserve">料理5*5種くらい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洋食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">和食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サイドメニュー</t>
   </si>
   <si>
     <t xml:space="preserve">タブ画像</t>
@@ -156,6 +165,24 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">ビーフステーキ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すき焼き膳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポテトフライ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ビーフシチュー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天ぷら御膳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニオンリング</t>
+  </si>
+  <si>
     <t xml:space="preserve">ListBox</t>
   </si>
   <si>
@@ -163,6 +190,33 @@
   </si>
   <si>
     <t xml:space="preserve">注文一覧、会計確認一覧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">チキンステーキ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">焼き魚定食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バターコーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ハンバーグステーキ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魚の煮つけ定食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミニサイズピザ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスタ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天ざるセット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唐揚げ4個</t>
   </si>
   <si>
     <t xml:space="preserve">Label</t>
@@ -725,7 +779,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -760,21 +814,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -783,13 +822,6 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -822,20 +854,6 @@
     </font>
     <font>
       <u val="single"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1012,72 +1030,76 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1085,23 +1107,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1139,14 +1161,14 @@
       <rgbColor rgb="FFFFFFFF"/>
       <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000EE"/>
+      <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF006600"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF996600"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -1310,1180 +1332,1216 @@
   <dimension ref="A1:K77"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="1" style="0" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="1" style="1" width="12.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1"/>
-      <c r="B34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1"/>
-      <c r="B50" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1"/>
-      <c r="B54" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="A54" s="2"/>
+      <c r="B54" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1"/>
-      <c r="B61" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" s="1"/>
-      <c r="D61" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1"/>
-      <c r="B64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1"/>
-      <c r="B65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
+      <c r="A65" s="2"/>
+      <c r="B65" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1"/>
-      <c r="B67" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
+      <c r="A67" s="2"/>
+      <c r="B67" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1"/>
-      <c r="B72" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
+      <c r="A72" s="2"/>
+      <c r="B72" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/企画書＆仕様書/真仕様書.xlsx
+++ b/企画書＆仕様書/真仕様書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t xml:space="preserve">仕様書</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t xml:space="preserve">料理5*5種くらい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洋食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">和食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サイドメニュー</t>
   </si>
   <si>
     <t xml:space="preserve">タブ画像</t>
@@ -156,6 +165,24 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">ビーフステーキ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">すき焼き膳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポテトフライ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ビーフシチュー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天ぷら御膳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニオンリング</t>
+  </si>
+  <si>
     <t xml:space="preserve">ListBox</t>
   </si>
   <si>
@@ -165,6 +192,33 @@
     <t xml:space="preserve">注文一覧、会計確認一覧</t>
   </si>
   <si>
+    <t xml:space="preserve">チキンステーキ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">焼き魚定食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バターコーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ハンバーグステーキ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魚の煮つけ定食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミニサイズピザ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスタ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天ざるセット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唐揚げ4個</t>
+  </si>
+  <si>
     <t xml:space="preserve">Label</t>
   </si>
   <si>
@@ -301,7 +355,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">タブ</t>
+    <t xml:space="preserve">タグ</t>
   </si>
   <si>
     <r>
@@ -411,7 +465,133 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">大フラグ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">タグ確認フラグ　1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザー操作</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">Bool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">型？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">なら操作可能</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">プログラムのフローチャート想定</t>
+  </si>
+  <si>
     <t xml:space="preserve">起動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイトル画像表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">picture1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prg = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面クリックでショップフローへ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gameflag = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prg = 1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ユーザー操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">OFF</t>
+    </r>
   </si>
   <si>
     <r>
@@ -436,42 +616,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">メニュータブ（Button）＊５</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料理画像（pictureBox)＊５</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料理名ラベル（Label）＊５</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料理名テキスト（Textbox）Visible = false;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">個数選択（nameric) Visible = false;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料金ラベル(Label) Visible = false;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計金額テキストボックス（TextBox) Visible = false;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文カゴに入れるボタン（Button） Visible=false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文カゴ(ListBox)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">席番号９９（Label)　（飾り)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">店員を呼ぶボタン（Button）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文確定ボタン（Button）</t>
-  </si>
-  <si>
+    <t xml:space="preserve">pictureshopBG pictureSelect pictureItemWindow</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">ユーザー操作</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -480,7 +637,58 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">MenuStatus = 1; </t>
+      <t xml:space="preserve">ON</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Gameflag = 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">料理選択</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注文リストへ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CartList.Add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入ボタンを押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BayButtonClicked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所持金チェック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money &gt; TotalCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">購入メッセージ表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所持金不足メッセージ表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MessageLabel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">shopMassage</t>
     </r>
     <r>
       <rPr>
@@ -490,8 +698,10 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">初期値は</t>
-    </r>
+      <t xml:space="preserve">ファイル読み込み</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -500,7 +710,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">Mybag</t>
     </r>
     <r>
       <rPr>
@@ -510,31 +720,18 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">＝洋食扱い</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">タブの選択情報</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,洋食</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,和食</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.サイドメニュー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.デザート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.ドリンク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プログラムのフローチャート想定</t>
-  </si>
-  <si>
+      <t xml:space="preserve">リストに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">MyCart</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -543,7 +740,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">料理カテゴリ</t>
+      <t xml:space="preserve">の物を</t>
     </r>
     <r>
       <rPr>
@@ -553,153 +750,26 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">(MenuStatus)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">に基づいて</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">１～５番の画像を指定の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">PictureBox</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">FoodMenu01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">05)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">で表示を切り替える</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">※1-01にはビーフステーキ、2-01にはすき焼き御膳という感じに</t>
-  </si>
-  <si>
-    <t xml:space="preserve">各種情報はdata.csvファイルにまとめる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内容は、ID,料理名,価格,画像ファイル名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タブ選択</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MenuStatus の情報に紐づいた情報で画像とテキスト表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料理名と料理画像の更新、選択中に表示される料理名と金額の非表示化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料理画像クリック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カテゴリとクリック画像に基づいた料理名と値段の表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menu0*Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文カゴに入れるボタン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">選択している料理情報を注文カゴリストボックスに表示する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">料理名テキストと個数、値段表示(Visible)を非表示にする（false)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計金額表示テキストボックスを表示する( true)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalOrderPriceテキストボックス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文カゴListBoXに入っている料理の金額を合計した値を表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文確定ボタン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メッセージボックスを表示＋会計SEを鳴らして、会計終わった表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">注文カゴListBoxに入っている情報をテキストファイルに出力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">店員を呼ぶボタン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メッセージボックス＋チャイムSEを再生</t>
-  </si>
-  <si>
-    <t xml:space="preserve">店員読んでますメッセージ表示する</t>
+      <t xml:space="preserve">Add</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">まだ買う？確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">買い物するボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">移動ボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prg = 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShoppingButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoveButton</t>
   </si>
 </sst>
 </file>
@@ -709,7 +779,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -838,6 +908,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="128"/>
@@ -1046,7 +1123,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1139,49 +1216,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>702720</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>122760</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>102960</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="画像 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5842440" y="7927200"/>
-          <a:ext cx="7314840" cy="4558320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1295,7 +1329,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="1" style="1" width="12.15"/>
@@ -1521,26 +1555,38 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="K15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="K16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1551,28 +1597,40 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="K17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="K18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1583,9 +1641,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1596,18 +1660,24 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1632,13 +1702,13 @@
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1677,7 +1747,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1692,13 +1762,13 @@
     <row r="27" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -1711,13 +1781,13 @@
     <row r="28" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1731,10 +1801,10 @@
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1748,10 +1818,10 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -1789,10 +1859,10 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1806,10 +1876,10 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -1836,7 +1906,7 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1851,13 +1921,13 @@
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -1871,10 +1941,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -1886,9 +1956,15 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -1899,8 +1975,12 @@
     </row>
     <row r="40" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="3"/>
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -1925,7 +2005,9 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
-      <c r="B42" s="0"/>
+      <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -1952,7 +2034,7 @@
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -1964,11 +2046,9 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
-      <c r="B45" s="10" t="s">
-        <v>44</v>
-      </c>
+      <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -1982,12 +2062,16 @@
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="E46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -1996,9 +2080,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2009,27 +2091,31 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="0"/>
-      <c r="F48" s="3"/>
+      <c r="E48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -2039,14 +2125,16 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
-      <c r="B50" s="0" t="s">
-        <v>49</v>
+      <c r="B50" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="3"/>
+      <c r="E50" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -2054,11 +2142,9 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
-      <c r="B51" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -2069,14 +2155,16 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="E52" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -2084,11 +2172,9 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -2099,14 +2185,14 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
-      <c r="B54" s="2" t="s">
-        <v>53</v>
+      <c r="B54" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="3"/>
+      <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -2114,14 +2200,12 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
-      <c r="B55" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="3"/>
+      <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -2129,14 +2213,16 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="3"/>
+      <c r="E56" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -2144,14 +2230,12 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
-      <c r="B57" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="3"/>
+      <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -2161,10 +2245,14 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
+      <c r="E58" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -2172,12 +2260,12 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
-      <c r="B59" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -2190,11 +2278,13 @@
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="E60" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -2202,14 +2292,16 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
-      <c r="B61" s="2" t="s">
-        <v>59</v>
+      <c r="B61" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="3"/>
+      <c r="D61" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -2217,11 +2309,9 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
-      <c r="B62" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -2232,14 +2322,16 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="3"/>
+      <c r="D63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -2247,13 +2339,15 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
-      <c r="B64" s="2" t="s">
-        <v>62</v>
+      <c r="B64" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="D64" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -2262,14 +2356,16 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
-        <v>63</v>
+      <c r="B65" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -2277,11 +2373,11 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
-      <c r="B66" s="3"/>
+      <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="3"/>
+      <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -2290,10 +2386,10 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
-      <c r="B67" s="2" t="s">
-        <v>64</v>
+      <c r="B67" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -2305,7 +2401,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2318,10 +2414,10 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2333,11 +2429,9 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
-      <c r="B70" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -2348,14 +2442,18 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="D71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -2363,13 +2461,15 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
-      <c r="B72" s="2" t="s">
-        <v>68</v>
+      <c r="B72" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="D72" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -2378,11 +2478,9 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
-      <c r="B73" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
@@ -2393,7 +2491,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -2406,11 +2504,9 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
-      <c r="B75" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -2421,11 +2517,9 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
-      <c r="B76" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -2436,11 +2530,9 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
-      <c r="B77" s="0" t="s">
-        <v>72</v>
-      </c>
+      <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
@@ -2451,157 +2543,6 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0.39375" bottom="0.39375" header="0" footer="0"/>
@@ -2610,6 +2551,5 @@
     <oddHeader>&amp;C&amp;"Arial,標準"&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Arial,標準"ページ &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>